--- a/MAJSushiConfig/ig/FRObservationPregnancyLMCDAFHIR.xlsx
+++ b/MAJSushiConfig/ig/FRObservationPregnancyLMCDAFHIR.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/ConceptMap/FRObservationPregnancyLMCDAFHIR</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/ConceptMap/FRObservationPregnancyLMCDAFHIR</t>
   </si>
   <si>
     <t>Version</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:25:17+00:00</t>
+    <t>2026-09-07T11:26:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -106,7 +106,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMPregnancyObservation</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMPregnancyObservation|0.1.0</t>
   </si>
   <si>
     <t/>

--- a/MAJSushiConfig/ig/FRObservationPregnancyLMCDAFHIR.xlsx
+++ b/MAJSushiConfig/ig/FRObservationPregnancyLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="73">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T11:26:50+00:00</t>
+    <t>2026-09-07T11:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -223,10 +223,16 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
+    <t>Observation / FRObservationLaboratoryReportResultsDocument / FRImagingStudyDocument</t>
+  </si>
+  <si>
     <t>FRLMPregnancyObservation.hasMember[x]</t>
   </si>
   <si>
     <t>Observation.hasMember</t>
+  </si>
+  <si>
+    <t>FRObservationLaboratoryReportResultsDocument / Observation</t>
   </si>
 </sst>
 </file>
@@ -671,7 +677,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -864,59 +870,24 @@
       <c r="D14" t="s" s="2">
         <v>68</v>
       </c>
-      <c r="E14" s="2"/>
+      <c r="E14" t="s" s="2">
+        <v>69</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D16" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D17" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D18" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="E18" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>72</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
